--- a/docs/triton-learning/cards/triton-lesson-10-block-scaled-matmul-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-10-block-scaled-matmul-correction.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -46,7 +46,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课节点 2 检查题：一张激活张量每行近似服从均值为 0 的正态分布；同事提议用 E3M0（非负值 0、0.25、0.5、1、2、4、8、16，约 6 档）代替 E2M1（约 3.58 档）。两种格式都按块最大值取 scale 时比较精度。</t>
+          <t xml:space="preserve">一张激活张量每行近似服从均值为 0 的正态分布；同事提议用 E3M0（非负值 0、0.25、0.5、1、2、4、8、16，约 6 档）代替 E2M1（约 3.58 档）。两种格式都按块最大值取 scale 时比较精度。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -77,7 +77,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课练习：MXFP4 量化规则写“e = ⌊log₂(amax)⌋ − 2，截到 \[−127, 127\]，scale 字节 = e + 127”，学习者对截断范围有疑问。</t>
+          <t xml:space="preserve">写 MXFP4 量化器时，规则是“e = ⌊log₂(amax)⌋ − 2，截到 \[−127, 127\]，scale 字节 = e + 127”，学习者对截断范围有疑问。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -108,7 +108,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课节点 3 答疑：块 scale 可以乘在输入元素上、部分和上或 MMA 指令内部；这里讨论没有指令内缩放、只有 FP8 等低精度 MMA 的硬件。</t>
+          <t xml:space="preserve">块 scale 可以乘在输入元素上、部分和上或 MMA 指令内部；这里讨论没有指令内缩放、只有 FP8 等低精度 MMA 的硬件。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -126,7 +126,6 @@
           <t xml:space="preserve">[T#B,!36b59d#结论]：方向对，但缺一个前提和一个例外。
 • [T#B#前提]：一条 MMA 算出的部分和不能跨 scale 块：Hopper 的 FP8 WGMMA 每条 K = 32，NVFP4 的 V = 16 就做不到。
 • [T#B#例外]：E2M1 的值乘 2^s，s 在 −8 到 6 之间时在 E4M3 里仍然精确；可以把每块的 scale 拆成“一个 K 块内的公共指数 × 相对部分”，相对部分乘在元素上，公共部分每个 K 块乘一次部分和。
-• [T#B#取舍]：没有低精度 MMA 时默认乘在元素上；要不要改，看多出的乘法、是否打乱 MMA 主循环、数值范围、访存还是计算受限、MMA 自身的累加精度。
 [T#B,!c47f17#边界]：拆指数的做法要求同一 K 块里各块的指数落在约 15 档的窗口内，超出的块会损失精度；这是可行性分析，没有核实哪个系统这样做。</t>
         </is>
       </c>
@@ -139,12 +138,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课节点 4 检查题：假设 TMEM 的格子从 32 位变成 64 位，物理形状变成 \[M/128, K/V/8, 32, 4, 8\]；问 kernel 里 trans(0, 3, 2, 1, 4) 的维度顺序要不要改、为什么。</t>
+          <t xml:space="preserve">Triton 3.7.1 的 sm_100 块缩放教程把 scale 预排成 \[M/128, K/V/4, 32, 4, 4\]，kernel 里用 reshape、trans(0, 3, 2, 1, 4)、reshape 还原。假设 TMEM 的格子从 32 位变成 64 位，物理形状变成 \[M/128, K/V/8, 32, 4, 8\]；问 trans(0, 3, 2, 1, 4) 的维度顺序要不要改、为什么。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">trans 不读写数据，它让最后一次 reshape 合出的下标正好是 tl.dot_scaled 要的行号 32g + r 和列号 4kc + c；访存是否连续，在定物理排法时就定了。</t>
+          <t xml:space="preserve">trans 不读写数据，它让最后一次 reshape 合出的下标正好是 tl.dot_scaled 要的行号 32g + r 和列号 8kc + c（64 位格子一格装 8 个 scale）；访存是否连续，在定物理排法时就定了。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -155,7 +154,7 @@
       <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：结论（不用改）和“让行、列的数位各自挨在一起”都对，“为了更好的连续访存”不对：sm_100 上它只是 SMEM 描述符上的一个视图。
-• [T#B#漏掉]：把 \[1, 4, 32, 4, 4\] 直接 reshape 成 \[128, 16\]，行号变成 32·kc + r、列号变成 4g + c：逻辑位置 (37, 10) 会取到第 69 行第 6 列的 scale，结果算错而不是变慢。
+• [T#B#漏掉]：以原来的 32 位布局为例：把 \[1, 4, 32, 4, 4\] 直接 reshape 成 \[128, 16\]，行号变成 32·kc + r、列号变成 4g + c，逻辑位置 (37, 10) 会取到第 69 行第 6 列的 scale，结果算错而不是变慢。
 • [T#B#写错]：块内排法换成 (g, r, c) 后应写 trans(0, 2, 3, 1, 4)；照抄旧的 trans，各维大小的乘积不变，照样能编译通过，只有数值核对抓得到。
 [T#B,!c47f17#边界]：漏掉或写错 trans 还会让编译器认不出这串写法，退回通用路径。</t>
         </is>
@@ -169,7 +168,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课综合验收：权重存 bf16（方式 A）对存 MXFP4 并在 kernel 里解码（方式 B）；负载分解码（每个专家 M = 8）和预填充（M = 4096）两种。</t>
+          <t xml:space="preserve">MI300X 上的 MoE 专家权重：存 bf16（方式 A）对存 MXFP4、在 kernel 里解码后仍用 bf16 MFMA（方式 B）；负载分解码（每个专家 M = 8）和预填充（M = 4096）两种，学习者估算时取 N = K = 1000。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -185,7 +184,7 @@
       <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：少读字节在预填充时换不来时间：这时受计算限制，而且例子里激活和输出各 8 MB、权重只有 2 MB，B 只少读约 8%。
-• [T#B#预填充]：B 最多和 A 一样快，剩下只看解码能不能藏进 MFMA；说“看访存效率和解码的权衡”也不准确。
+• [T#B#预填充]：B 最多和 A 一样快，剩下只看解码能不能藏进 MFMA。
 • [T#B#容量]：8 张 MI300X 跑 DeepSeek-V3：全部 bf16 只剩约 194 GB 显存，路由专家改存 MXFP4 后剩约 1150 GB，能放 KV cache 的显存约是原来的 6 倍；并发多了，解码时每个专家分到的 token 也多，计算强度随之升高。
 [T#B,!c47f17#边界]：解码负载下 B 更快的判断对，但前提是解码速度跟得上显存带宽。</t>
         </is>
@@ -194,17 +193,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">判断一个矩阵乘受访存还是计算限制时，统一计算强度和平衡点的单位。</t>
+          <t xml:space="preserve">用计算强度判断 MI300X 上一个 MoE 专家的矩阵乘（权重存 MXFP4）受访存还是计算限制，并说明算出的强度该怎样和平衡点比较。</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课综合验收复查：MI300X，DeepSeek-V3 式路由下每个专家 M = 128、N = K = 1024，权重存 MXFP4；平衡点按 bf16 稠密峰值与带宽算约 247 FLOP/字节，即约 123 次乘加/字节。</t>
+          <t xml:space="preserve">MI300X 的 bf16 稠密峰值 1307.4 TFLOPS、显存带宽 5.3 TB/s，平衡点约 247 FLOP/字节。DeepSeek-V3 式路由下每个专家 M = 128，权重 N = K = 1024 存 MXFP4（每 32 个 FP4 配 1 字节 scale），激活和输出都是 bf16。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">M·N·K ÷ 字节的单位是“次乘加/字节”，要和 123 比；按 FLOP 算要再乘 2，才和 247 比。这里 MXFP4 的 163.8 次乘加/字节已经越过平衡点，受计算限制。</t>
+          <t xml:space="preserve">M·N·K ÷ 字节得到的是“次乘加/字节”，要和约 123 次乘加/字节比；按 FLOP 算要再乘 2，才和 247 比。字节计入激活、权重、scale 和 bf16 输出后，这里约 124 次乘加/字节，几乎正好落在平衡点上，访存和计算两种限制都要考虑。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -214,9 +213,10 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：规格表的 TFLOPS 把一次乘加算 2 次运算（1307.4 TFLOPS 就是每秒 653.7 万亿次乘加），分子只写 M·N·K 时得到的是乘加次数。
-• [T#B#影响]：bf16 方式的 56.9 比 123 和 247 都低，结论碰巧不变；MXFP4 的 163.8 正好落在两者之间，单位一混，瓶颈就判反了。
-• [T#B#做法]：每个强度都写上单位，平衡点只用一种：按乘加是 123，按 FLOP 是 247。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在比较的单位：规格表的 TFLOPS 把一次乘加算 2 次运算（1307.4 TFLOPS 就是每秒 653.7 万亿次乘加），163.84 是次乘加/字节，拿它和 247 FLOP/字节比，等于把平衡点抬高了一倍。
+• [T#B#输出字节]：原式和原题都没计入 bf16 输出的 262,144 字节（题目让先忽略激活和输出），这一项不算原答的错。计入后分母是 1,081,344 字节，134,217,728 ÷ 1,081,344 ≈ 124.1；输出若为 fp32，约 99.9，低于平衡点。
+• [T#B#影响]：bf16 方式计入输出后约 51.2，比 123 和 247 都低，单位混用碰巧不改变结论；落在 123 和 247 之间的强度，单位一混就会判错。
+• [T#B#做法]：每个强度都写上单位，平衡点只用一种：按乘加是 123，按 FLOP 是 247；字节要计入输入、scale 和输出。
 [T#B,!c47f17#边界]：规格表里的稀疏 TFLOPS 是稠密值的 2 倍，估算稠密 GEMM 时不能用。</t>
         </is>
       </c>
@@ -224,17 +224,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">判断 MXFP4 权重的解码开销相对 MFMA 的比例是否随 M 变化。</t>
+          <t xml:space="preserve">说明每个专家 M = 128 时，M 的大小怎样影响 MXFP4 权重的解码能否藏进 MFMA，并据此判断方式 B 会不会比方式 A 慢。</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课综合验收复查：MI300X，bf16 激活 × MXFP4 权重，每个专家 M = 128，BLOCK_M = 128，8 个 wave 全沿 N 排（每个权重元素在 CTA 内只解码一次）；按 bf16 存的方式受访存限制，用时约 2.2T（T 是 MFMA 按峰值算完的时间）。</t>
+          <t xml:space="preserve">MI300X，bf16 激活 × 权重 N = K = 1024，BLOCK_M = 128，8 个 wave 全沿 N 排（每个权重元素在 CTA 内只解码一次）；每个专家 M = 4096 时，按编译产物估，解码约为 MFMA 时间的 43%。现在每个专家只分到 M = 128：方式 A 存 bf16 权重，受访存限制，用时约 2.4T；方式 B 存 MXFP4、在 kernel 里解码，访存约 0.99T。T 是 MFMA 按峰值算完的时间，访存与计算按重叠估。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">解码相对 MFMA 的比例是 16c / BLOCK_M（c 是每个 FP4 的向量指令数），与 M 无关：M = 128 时解码占比和 M = 4096 时一样，约 43%。MXFP4 方式受计算限制，用时 1T 到 1.43T，仍比 bf16 快约 1.5 到 2.2 倍。</t>
+          <t xml:space="preserve">解码相对 MFMA 的比例是 16c / BLOCK_M（c 是每个 FP4 的向量指令数），与 M 无关：M = 128 时和 M = 4096 时一样约 43%。B 用时 1T（解码全藏住）到 1.43T（全藏不住），仍比 A 的约 2.4T 快约 1.7 到 2.4 倍。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -244,9 +244,9 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：每个 CTA 把自己那块权重解码一次，每个解码出的 FP4 和这个 CTA 的 BLOCK_M 行各做一次乘加：解码总量是 N·K·cdiv(M, BLOCK_M)，乘加总量是 cdiv(M, BLOCK_M)·BLOCK_M·N·K，相除只剩 BLOCK_M。
-• [T#B#比较]：“藏不住”只说明 B 要多花时间，要把总时间算出来再和 A 比。
-• [T#B#为何到不了 3.8 倍]：B 越过了平衡点，用时由 MFMA 决定，就算解码不花时间，也最多快 2.2 倍。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在把“藏不住”归因于 M 小：每个 CTA 把自己那块权重解码一次，每个解码出的 FP4 和这个 CTA 的 BLOCK_M 行各做一次乘加，解码总量 N·K·cdiv(M, BLOCK_M)，乘加总量 cdiv(M, BLOCK_M)·BLOCK_M·N·K，相除只剩 BLOCK_M。
+• [T#B#比较]：“藏不住”只说明 B 要多花时间，要把总时间算出来再和 A 比：B 最慢也只是 1.43T；访存与计算不重叠时，A 约 3.4T、B 约 2.0T 到 2.4T，B 仍更快。
+• [T#B#为何到不了 3.8 倍]：激活和输出的字节不会变少，总字节只少约 2.4 倍；B 的访存约 0.99T，已和 MFMA 的 1T 相当，就算解码不花时间，也最多快约 2.4 倍。
 [T#B,!c47f17#边界]：只有 M 小于 BLOCK_M 时 M 才起作用：补齐的行让 MFMA 白算，解码只摊到 M 行有效的乘加上。</t>
         </is>
       </c>
@@ -254,12 +254,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">解释量化代码里用 torch.pow(2, -e) 求 2^(−e) 时，结果为什么是 0，并指出同类的整数陷阱。</t>
+          <t xml:space="preserve">解释量化代码里用 torch.pow(2, -e) 求 2^(−e) 时，结果为什么是 0。</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课练习：一块数的 amax 是 15.6875，e = 1，存在 int32 张量里；计算 data * torch.pow(2, -1*e) 时，整块变成 0 和 −0。</t>
+          <t xml:space="preserve">在 PyTorch 2.13.0 中写 MXFP4 量化：一块数的 amax 是 15.6875，e = 1，存在 int32 张量里；计算 data * torch.pow(2, -1*e) 时，整块变成 0 和 −0。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -276,7 +276,7 @@
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：PyTorch 的类型提升规则：Python 标量只有在类别高于张量时才改变结果的 dtype，int 标量和 int 张量运算，结果仍是 int。
 • [T#B#不报错]：torch.tensor(2) ** -1 会报错，但指数是张量时直接给出 0，相当于 C 里用 int 算 1/2；负数乘 +0 显示为 −0。
-• [T#B#同类]：uint8 的 scales − 127 会回绕：\[120, 127, 130\] 减 127 得到 \[249, 0, 3\]，要先转成 float32 或 int32 再减。
+• [T#B#同类陷阱（延伸）]：uint8 的 scales − 127 会回绕：\[120, 127, 130\] 减 127 得到 \[249, 0, 3\]，要先转成 float32 或 int32 再减。
 [T#B,!c47f17#边界]：遇到整数和浮点混算的怪结果，先打印 .dtype。</t>
         </is>
       </c>
@@ -284,12 +284,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">区分块缩放 kernel 里“块宽”和“前进量”两种 BLOCK_K // 2，并说明把前进量误写成 BLOCK_K 会发生什么、测试怎样才能抓到。</t>
+          <t xml:space="preserve">判断块缩放 kernel 里把每个 K 步的前进量 BLOCK_K // 2 误写成 BLOCK_K 会发生什么，以及测试怎样才能抓到这种错。</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课 A6：一个 K 步处理 BLOCK_K 个 FP4 元素；packed 每步前进 BLOCK_K // 2 字节，scale 前进 BLOCK_K // 32。学习者在 GPU 上把它们改成 BLOCK_K 试验，第一次实测得到编译错误 lhs_scale must be a tensor of shape \[..., 128, 8\]。</t>
+          <t xml:space="preserve">块缩放 kernel 一个 K 步处理 BLOCK_K 个 FP4 元素；packed 每步前进 BLOCK_K // 2 字节，scale 前进 BLOCK_K // 32。学习者在 GPU 上把代码改成 BLOCK_K 试验，第一次实测得到编译错误 lhs_scale must be a tensor of shape \[..., 128, 8\]。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -304,7 +304,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：第一次改的是块宽（tl.arange 的长度，决定张量形状，dot_scaled 在编译时检查），所以报编译错误；A6 问的是前进量 k_id * BLOCK_K // 2，它决定第 k 步从哪个字节开始读。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：第一次改的是块宽（tl.arange 的长度，决定张量形状，dot_scaled 在编译时检查），所以报编译错误；题目问的是前进量 k_id * BLOCK_K // 2，它决定第 k 步从哪个字节开始读。
 • [T#B#测试]：只有一个 K 步的用例里 k_id = 0，系数写错也看不出来；要抓前进量的错，测试必须有多个 K 步。
 • [T#B#inf 和 nan]：读错位置拿到的 scale 字节是随机的 2 的幂：255 就是 NaN，接近 254 的是 2¹²⁷ 量级，乘出来溢出成 inf，inf 和 −inf 相加又得 NaN。
 [T#B,!c47f17#边界]：越界读多半不崩溃：缓存分配器按大块申请显存，读过张量末尾一点，多半仍落在已映射的内存里，表现为悄悄算错。</t>
@@ -319,7 +319,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课 V1：MXFP6（E3M2）每个编码 6 位，约定把每行看成一条小端位流：第 i 个元素占第 6i 到 6i+5 位，位流第 b 位放在第 ⌊b/8⌋ 个字节的第 b mod 8 位。以编码 1、2、3、4 为例，字节写成最高位在左。</t>
+          <t xml:space="preserve">MXFP6（E3M2）每个编码 6 位，约定把每行看成一条小端位流：第 i 个元素占第 6i 到 6i+5 位，位流第 b 位放在第 ⌊b/8⌋ 个字节的第 b mod 8 位。以编码 1、2、3、4 为例，字节写成最高位在左。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -349,7 +349,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课 M1：同一个 MXFP4 kernel 去掉 A 的 scale，迫使 sm_120 走软件换算（A、B 的 FP4 都解码成 bf16），N = K = 8192，M = 16 与 M = 8192；学习者在运行前写预测，T 是 BF16 矩阵乘按峰值算完的时间。</t>
+          <t xml:space="preserve">RTX 5090（sm_120）、Triton 3.7.1：同一个 MXFP4 kernel 去掉 A 的 scale，迫使 sm_120 走软件换算（A、B 的 FP4 都解码成 bf16），N = K = 8192，M = 16 与 M = 8192；学习者在运行前写预测，T 是 BF16 矩阵乘按峰值算完的时间。</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -365,9 +365,10 @@
       <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：按 128 次算，等于把 BLOCK_M 当成了复用次数；按实际的 5.3 次，M = 16 时解码时间约为 1.6T，是估计的 30 倍。
+• [T#B#式子]：原式的结构是 (每个元素的向量指令数 ÷ 向量单元的速率) ÷ (复用次数 ÷ 张量核的速率)：52.4 是 RTX 5090 每秒约 52.4 万亿条 lane 指令，104.75 是 BF16 张量核每秒约 104.75 万亿次乘加。
 • [T#B#单价]：每个元素约 4 条线程级指令，和沿用的 3.5 条差不多：单价没估错，错在复用次数。
 • [T#B#结果]：实测比值 M = 16 为 1.570、M = 8192 为 4.368，预测的 \[0.99, 1.01\] 和 \[7.8, 8.2\] 都被否定。
-• [T#B#其他假设]：还默认了几部分完全重叠、两条路径都能跑到峰值；MB 再乘 1024² 与带宽取 1.75 TB/s 两处在比值里互相抵消。
+• [T#B#其他假设]：还默认了几部分完全重叠、两条路径都能跑到峰值。
 [T#B,!c47f17#边界]：复用次数要按每个 warp 的子块和实际要解码的操作数来数；M 很小时 Triton 还会交换操作数。</t>
         </is>
       </c>
@@ -380,7 +381,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课 M1，RTX 5090，M = 16：原生 0.0287 ms，按最少字节算 1263 GB/s；软件换算 0.0451 ms，804 GB/s；带宽峰值 1792 GB/s，软件路径还只用到 BF16 算力峰值的 22.7%。</t>
+          <t xml:space="preserve">RTX 5090、Triton 3.7.1，M = 16：原生 0.0287 ms，按最少字节算 1263 GB/s；软件换算 0.0451 ms，804 GB/s；带宽峰值 1792 GB/s，软件路径还只用到 BF16 算力峰值的 22.7%。</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -397,7 +398,7 @@
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：这是循环论证：结果本身被当成了原因。
 • [T#B#线索]：两种资源都没跑满，说明卡住它的既不是显存，也不是张量核，要找第三种资源。
-• [T#B#证据]：SASS 计数：软件路径每个 warp 每个 K 步 1842 条指令（原生 166 条），最忙的 SM 上发射约 24.5 µs，加上搬最少字节的 20.2 µs 约 44.7 µs，接近实测的 45.1 µs。
+• [T#B#证据]：SASS 计数：软件路径每个 warp 每个 K 步 1842 条指令（原生 166 条），最忙的 SM 上发射约 24.5 µs，加上搬最少字节的 20.2 µs 约 44.7 µs，接近实测的 45.1 µs；这是静态估算，没有 profiler 数据证实。
 [T#B,!c47f17#边界]：“最少字节 ÷ 时间”也不是实测的显存流量，实际流量只会更多。</t>
         </is>
       </c>
@@ -410,12 +411,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课 M1，M = 8192：原生 1.379 ms（FP4 峰值的 47.6%），软件换算 6.010 ms（BF16 峰值的 87.3%），比值 4.368；选配置那一段输出里，有几个软件候选寄存器溢出。</t>
+          <t xml:space="preserve">RTX 5090、Triton 3.7.1，M = 8192：原生 1.379 ms（FP4 峰值的 47.6%），软件换算 6.010 ms（BF16 峰值的 87.3%），比值 4.368；选配置那一段输出里，有几个软件候选寄存器溢出。</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">计算受限时，比值 = 峰值比 × 效率比 = 8 × (47.6% ÷ 87.3%) ≈ 4.4；溢出出现在没被选中的配置上，选中的软件配置 128 × 64 × 64 用 229 个寄存器，没有溢出。</t>
+          <t xml:space="preserve">计算受限时，比值 = 峰值比 × 效率比 = 8 × (47.6% ÷ 87.3%) ≈ 4.4：原生只到 FP4 峰值的一半不到；看到的寄存器溢出出在没被选中的配置上，选中的软件配置用 229 个寄存器，没有溢出。</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -426,7 +427,7 @@
       <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：比值低，是因为原生路径只到了 FP4 峰值的一半不到，而软件路径的解码完全藏在较慢的 BF16 张量核后面。
-• [T#B#原生的缺口]：张量核 0.66 ms、发射 0.20 ms、显存 0.19 ms，相加 1.05 ms，实测 1.38 ms；多出的约 0.33 ms 分不出来源，可能是 2 级流水加每 SM 1 个 CTA 的空泡、运行时的频率与功耗，或这条指令本来就到不了白皮书的峰值。
+• [T#B#原生的缺口]：原生路径的张量核、发射、显存三部分相加约 1.05 ms，实测 1.38 ms，多出的约 0.33 ms 目前分不出来源；要用 Nsight Compute 看张量核的忙碌比例与 warp 停顿原因、记录运行时频率与功耗，或单测 OMMA 的小 kernel 来分辨。
 • [T#B#规律]：张量核越快，同样的额外开销占比越大，所以峰值比只是上限。
 [T#B,!c47f17#边界]：脚本先在同一组候选里挑最快的配置，正是为了不让哪条路径因为配置选得差而吃亏；读溢出信息前，先确认它是不是被测的那个配置。</t>
         </is>
@@ -440,7 +441,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课节点 1：理解浮点公式时，学习者用“指数找 2 的幂、尾数在两个 2 的幂之间表示数”的直觉来读公式。</t>
+          <t xml:space="preserve">初学浮点表示时，学习者用“指数找 2 的幂、尾数在两个 2 的幂之间表示数”的直觉来读这个公式。</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -470,7 +471,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课练习：quantize_mxfp4 返回 packed（FP4 编码）和 scales（E8M0 字节），kernel 里把 scales 交给 tl.dot_scaled。</t>
+          <t xml:space="preserve">Triton 3.7.1 与 PyTorch 2.13：quantize_mxfp4 返回 packed（FP4 编码）和 scales（E8M0 字节），kernel 里把 scales 交给 tl.dot_scaled。</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -487,9 +488,9 @@
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：两者位布局相同，scales.view(torch.float8_e8m0fnu) 只换解读、不动字节，但交给 Triton 时必须是 uint8。
 • [T#B#Triton]：dtype 映射表里没有 float8_e8m0fnu，这种张量传给 kernel，一发射就报 KeyError。
-• [T#B#转换]：.to(torch.float8_e8m0fnu) 是就近舍入，不是 OCP 的向下取：7.5 那一块会得到字节 128（scale 2），OCP 要的是 127。
+• [T#B#转换]：.to(torch.float8_e8m0fnu) 是就近舍入，不是 OCP 的向下取：amax = 7.5 的块，OCP 取 2^(⌊log₂ 7.5⌋ − 2) = 1（字节 127）；把 amax / 4 = 1.875 直接转成 float8_e8m0fnu，会舍入成 2（字节 128）。
 • [T#B#PyTorch]：torch._scaled_mm 反过来靠 scale 的 dtype 判断要不要走块缩放；两边之间用 view 来回切换，没有开销。
-[T#B,!c47f17#边界]：以上以 Triton 3.7.1 和 PyTorch 2.13 为准。</t>
+[T#B,!c47f17#边界]：需要 E8M0 的语义时，在 PyTorch 一侧用 view 切换解读，不要用 .to() 转换取值。</t>
         </is>
       </c>
     </row>
@@ -501,7 +502,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 10 课综合验收第二次复查：MI300X，bf16 激活 × MXFP4 权重，BLOCK_M = 32，N = K = 1024，8 个 wave 全沿 N 排。</t>
+          <t xml:space="preserve">MI300X，bf16 激活 × MXFP4 权重，BLOCK_M = 32，N = K = 1024，8 个 wave 全沿 N 排；沿用每个 FP4 的解码要 c = 3.5 条向量指令的估计。</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -519,37 +520,7 @@
           <t xml:space="preserve">[T#B,!36b59d#结论]：把 kernel 写成串行的 C 循环 acc\[m\]\[n\] += a\[m\]\[k\] * w\[k\]\[n\]：只有 (k, n) 等于它自己的下标时才用到它，这时 m 跑 BLOCK_M 个值。
 • [T#B#BM × K]：是权重的一整列（K 个元素）在这个 CTA 里合计参与的乘加数。
 • [T#B#影响]：解码相对乘加的比例 16c / BLOCK_M 正来自这个复用次数：BLOCK_M 从 128 降到 32，比值从约 0.43 升到约 1.75，就藏不住了。
-[T#B,!c47f17#边界]：若 M 方向有多个 wave（比如 warpsPerCTA = \[2, 4\]），每个 wave 各解码一份，每份只参与 BLOCK_M / 2 次乘加。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">把逐元素的“符号位为 1 才取负”改写成整张量运算时，正确地放回符号。</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">第 10 课 R-04：把 dequantize_mxfp4 的 Python 循环改成整张量运算；low、high 是解出的绝对值张量，low_sign、high_sign 是取值 0 或 1 的符号位张量。</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">要表达“符号位为 0 乘 1、为 1 乘 −1”，例如 low *= torch.where(low_sign == 1, -1, 1)。</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">low *= -low_sign；high *= -high_sign</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：符号位为 0 时乘的是 −0，所有正数都变成 −0.0：\[3.0, 1.5\] 配符号位 \[0, 1\]，得到 \[−0.0, −1.5\]。
-• [T#B#思路]：整张量改写和把 C 循环改成 SIMD 一样：分支改成两边都算、再按条件挑，torch.where 相当于 AVX 的 blend。
-• [T#B#另外两个坑]：uint8 的下标张量会被当成布尔掩码，要先转成 long；格点表要建在输入所在的设备上。
-[T#B,!c47f17#边界]：改写后先在随机输入上逐字节比较新旧两版的输出，确认完全一致。</t>
+[T#B,!c47f17#边界]：c = 3.5 来自一个超出 CDNA3 LDS 上限、跑不起来的编译配置；换成能运行的配置，c ≈ 3.25，比值约 1.63，结论不变。</t>
         </is>
       </c>
     </row>
